--- a/excel-files/LAS PINAS/LAS PIÑAS NORTH NATIONAL HIGH SCHOOL.xlsx
+++ b/excel-files/LAS PINAS/LAS PIÑAS NORTH NATIONAL HIGH SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29816"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="361" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D283939-00A6-4D7A-ADFF-99314146C00D}"/>
+  <xr:revisionPtr revIDLastSave="556" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AF30A0A-A368-416F-AA5D-889E5AC622B7}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -3715,7 +3715,7 @@
       <c r="N5" s="44"/>
       <c r="O5" s="45"/>
     </row>
-    <row r="6" spans="1:15" ht="19.149999999999999">
+    <row r="6" spans="1:15" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -3820,7 +3820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="19.149999999999999">
+    <row r="12" spans="1:15" ht="19.5">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -3945,7 +3945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="19.149999999999999">
+    <row r="19" spans="1:8" ht="19.5">
       <c r="A19" s="1">
         <v>3</v>
       </c>
@@ -4015,7 +4015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="19.149999999999999">
+    <row r="23" spans="1:8" ht="19.5">
       <c r="A23" s="1">
         <v>4</v>
       </c>
@@ -5474,8 +5474,8 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E2:E6 E8:E12 E14:E19 E21:E29 E31:E39 E41:E49 E51:E59 E61:E69 E71:E79 E81:E89" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -5493,7 +5493,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -5718,7 +5718,7 @@
       <c r="Z4" s="13"/>
       <c r="AA4" s="13"/>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999">
+    <row r="5" spans="1:27" ht="38.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -5787,7 +5787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999">
+    <row r="6" spans="1:27" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -5856,7 +5856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999">
+    <row r="7" spans="1:27" ht="19.5">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -5925,7 +5925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999">
+    <row r="8" spans="1:27" ht="19.5">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -5994,7 +5994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999">
+    <row r="9" spans="1:27" ht="19.5">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -6063,7 +6063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999">
+    <row r="10" spans="1:27" ht="19.5">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -6132,7 +6132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="19.149999999999999">
+    <row r="11" spans="1:27" ht="19.5">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -6201,7 +6201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="19.149999999999999">
+    <row r="12" spans="1:27" ht="19.5">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -6352,7 +6352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999">
+    <row r="15" spans="1:27" ht="19.5">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -6421,7 +6421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999">
+    <row r="16" spans="1:27" ht="19.5">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -6490,7 +6490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999">
+    <row r="17" spans="1:27" ht="19.5">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -6559,7 +6559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999">
+    <row r="18" spans="1:27" ht="19.5">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -6628,7 +6628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999">
+    <row r="19" spans="1:27" ht="19.5">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -6697,7 +6697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="19.149999999999999">
+    <row r="20" spans="1:27" ht="19.5">
       <c r="A20" s="1">
         <v>2</v>
       </c>
@@ -6766,7 +6766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="19.149999999999999">
+    <row r="21" spans="1:27" ht="19.5">
       <c r="A21" s="1">
         <v>2</v>
       </c>
@@ -6918,7 +6918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999">
+    <row r="24" spans="1:27" ht="19.5">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -6987,7 +6987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999">
+    <row r="25" spans="1:27" ht="19.5">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -7056,7 +7056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999">
+    <row r="26" spans="1:27" ht="19.5">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -7125,7 +7125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999">
+    <row r="27" spans="1:27" ht="19.5">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -7194,7 +7194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999">
+    <row r="28" spans="1:27" ht="19.5">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -7263,7 +7263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999">
+    <row r="29" spans="1:27" ht="19.5">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -7332,7 +7332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="19.149999999999999">
+    <row r="30" spans="1:27" ht="19.5">
       <c r="A30" s="1">
         <v>3</v>
       </c>
@@ -7401,7 +7401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="19.149999999999999">
+    <row r="31" spans="1:27" ht="19.5">
       <c r="A31" s="1">
         <v>3</v>
       </c>
@@ -7470,9 +7470,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J32" s="13"/>
-      <c r="M32" s="5"/>
       <c r="N32" s="13"/>
       <c r="O32" s="13"/>
       <c r="P32" s="13"/>
@@ -7484,7 +7483,7 @@
       <c r="Z32" s="13"/>
       <c r="AA32" s="13"/>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999">
+    <row r="33" spans="1:27" ht="19.5">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -7553,7 +7552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999">
+    <row r="34" spans="1:27" ht="19.5">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -7622,7 +7621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999">
+    <row r="35" spans="1:27" ht="19.5">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -7691,7 +7690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999">
+    <row r="36" spans="1:27" ht="19.5">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -7760,7 +7759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999">
+    <row r="37" spans="1:27" ht="38.25">
       <c r="A37" s="1">
         <v>4</v>
       </c>
@@ -7829,7 +7828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999">
+    <row r="38" spans="1:27" ht="19.5">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -7898,7 +7897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999">
+    <row r="39" spans="1:27" ht="19.5">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -7967,7 +7966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999">
+    <row r="40" spans="1:27" ht="19.5">
       <c r="A40" s="1">
         <v>4</v>
       </c>
@@ -8036,7 +8035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999">
+    <row r="41" spans="1:27" ht="19.5">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -8105,9 +8104,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J42" s="13"/>
-      <c r="M42" s="5"/>
       <c r="N42" s="13"/>
       <c r="O42" s="13"/>
       <c r="P42" s="13"/>
@@ -8188,7 +8186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999">
+    <row r="44" spans="1:27" ht="19.5">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -8257,7 +8255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="19.5">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -8326,7 +8324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999">
+    <row r="46" spans="1:27" ht="19.5">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -8395,7 +8393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="38.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -8464,7 +8462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999">
+    <row r="48" spans="1:27" ht="19.5">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -8533,7 +8531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999">
+    <row r="49" spans="1:27" ht="19.5">
       <c r="A49" s="1">
         <v>5</v>
       </c>
@@ -8602,7 +8600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999">
+    <row r="50" spans="1:27" ht="19.5">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -8671,7 +8669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999">
+    <row r="51" spans="1:27" ht="19.5">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -8823,7 +8821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="19.149999999999999">
+    <row r="54" spans="1:27" ht="19.5">
       <c r="A54" s="1">
         <v>6</v>
       </c>
@@ -8892,7 +8890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="19.149999999999999">
+    <row r="55" spans="1:27" ht="19.5">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -8961,7 +8959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999">
+    <row r="56" spans="1:27" ht="19.5">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -9030,7 +9028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999">
+    <row r="57" spans="1:27" ht="38.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -9099,7 +9097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999">
+    <row r="58" spans="1:27" ht="19.5">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -9168,7 +9166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999">
+    <row r="59" spans="1:27" ht="19.5">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -9237,7 +9235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999">
+    <row r="60" spans="1:27" ht="19.5">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -9306,7 +9304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999">
+    <row r="61" spans="1:27" ht="19.5">
       <c r="A61" s="1">
         <v>6</v>
       </c>
@@ -10969,7 +10967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J82" s="13"/>
       <c r="M82" s="5"/>
       <c r="N82" s="13"/>
@@ -12646,7 +12644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="19.5">
       <c r="A104" s="1" t="s">
         <v>29</v>
       </c>
@@ -12715,7 +12713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="19.5">
       <c r="A105" s="1" t="s">
         <v>29</v>
       </c>
@@ -12784,7 +12782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="19.5">
       <c r="A106" s="1" t="s">
         <v>29</v>
       </c>
@@ -12853,7 +12851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="38.450000000000003">
+    <row r="107" spans="1:27" ht="38.25">
       <c r="A107" s="1" t="s">
         <v>29</v>
       </c>
@@ -12922,7 +12920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="38.25">
       <c r="A108" s="1" t="s">
         <v>29</v>
       </c>
@@ -12991,7 +12989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="38.450000000000003">
+    <row r="109" spans="1:27" ht="57.75">
       <c r="A109" s="1" t="s">
         <v>29</v>
       </c>
@@ -13060,7 +13058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="38.450000000000003">
+    <row r="110" spans="1:27" ht="38.25">
       <c r="A110" s="1" t="s">
         <v>29</v>
       </c>
@@ -13202,7 +13200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="19.149999999999999">
+    <row r="113" spans="1:27" ht="19.5">
       <c r="A113" s="1"/>
       <c r="B113" s="9"/>
       <c r="C113" s="1"/>
@@ -13264,7 +13262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="19.149999999999999">
+    <row r="114" spans="1:27" ht="19.5">
       <c r="A114" s="1"/>
       <c r="B114" s="9"/>
       <c r="C114" s="1"/>
@@ -13326,7 +13324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="19.149999999999999">
+    <row r="115" spans="1:27" ht="19.5">
       <c r="A115" s="1"/>
       <c r="B115" s="9"/>
       <c r="C115" s="1"/>
@@ -13388,7 +13386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="19.149999999999999">
+    <row r="116" spans="1:27" ht="19.5">
       <c r="A116" s="1"/>
       <c r="B116" s="9"/>
       <c r="C116" s="1"/>
@@ -13450,7 +13448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="19.149999999999999">
+    <row r="117" spans="1:27" ht="19.5">
       <c r="A117" s="1"/>
       <c r="B117" s="9"/>
       <c r="C117" s="1"/>
@@ -13512,7 +13510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="19.149999999999999">
+    <row r="118" spans="1:27" ht="19.5">
       <c r="A118" s="1"/>
       <c r="B118" s="9"/>
       <c r="C118" s="1"/>
@@ -13574,7 +13572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="19.149999999999999">
+    <row r="119" spans="1:27" ht="19.5">
       <c r="A119" s="1"/>
       <c r="B119" s="9"/>
       <c r="C119" s="1"/>
@@ -13636,7 +13634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="19.149999999999999">
+    <row r="120" spans="1:27" ht="19.5">
       <c r="A120" s="1"/>
       <c r="B120" s="9"/>
       <c r="C120" s="1"/>
@@ -13698,7 +13696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="19.149999999999999">
+    <row r="121" spans="1:27" ht="19.5">
       <c r="A121" s="1"/>
       <c r="B121" s="9"/>
       <c r="C121" s="1"/>
@@ -13760,7 +13758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="19.149999999999999">
+    <row r="122" spans="1:27" ht="19.5">
       <c r="A122" s="1"/>
       <c r="B122" s="9"/>
       <c r="C122" s="1"/>
@@ -13822,7 +13820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="19.149999999999999">
+    <row r="123" spans="1:27" ht="19.5">
       <c r="A123" s="1"/>
       <c r="B123" s="9"/>
       <c r="C123" s="1"/>
@@ -13884,7 +13882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="19.149999999999999">
+    <row r="124" spans="1:27" ht="19.5">
       <c r="A124" s="1"/>
       <c r="B124" s="9"/>
       <c r="C124" s="1"/>
@@ -13946,7 +13944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="19.149999999999999">
+    <row r="125" spans="1:27" ht="19.5">
       <c r="A125" s="1"/>
       <c r="B125" s="9"/>
       <c r="C125" s="1"/>
@@ -14008,7 +14006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="19.149999999999999">
+    <row r="126" spans="1:27" ht="19.5">
       <c r="A126" s="1"/>
       <c r="B126" s="9"/>
       <c r="C126" s="1"/>
@@ -14070,13 +14068,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="19.149999999999999">
+    <row r="127" spans="1:27" ht="19.5">
       <c r="A127" s="29"/>
       <c r="B127" s="30"/>
       <c r="C127" s="29"/>
       <c r="D127" s="5"/>
       <c r="E127" s="31"/>
-      <c r="F127" s="29"/>
+      <c r="F127" s="1"/>
       <c r="G127" s="31"/>
       <c r="H127" s="5">
         <f t="shared" si="22"/>
@@ -14091,7 +14089,7 @@
         <v>0</v>
       </c>
       <c r="K127" s="31"/>
-      <c r="L127" s="29"/>
+      <c r="L127" s="1"/>
       <c r="M127" s="31"/>
       <c r="N127" s="5">
         <f t="shared" ref="N127" si="24">IF((J127-K127)&lt;0,0,(J127-K127))</f>
@@ -14103,7 +14101,7 @@
       </c>
       <c r="P127" s="5"/>
       <c r="Q127" s="31"/>
-      <c r="R127" s="29"/>
+      <c r="R127" s="1"/>
       <c r="S127" s="31"/>
       <c r="T127" s="5">
         <f t="shared" si="18"/>
@@ -14129,191 +14127,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12" name="Textbooks"/>
-    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13" name="LAS"/>
-    <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" name="SOURCE"/>
+    <protectedRange sqref="J2:L3 D2:F3 H5:L5 W14:X21 W23:X31 H33:I41 W33:X41 H43:I51 W43:X51 H53:I61 W53:X61 H63:I71 W63:X71 H73:I81 W73:X81 H83:I91 W83:X91 H93:I101 W93:X101 H103:I110 W103:X110 H112:I127 N127:Q127 W112:X127 H14:I21 H23:I31 H6:I12 Q112:R112 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 D5:F12 D14:F21 D23:F31 D33:F41 D43:F51 D53:F61 D63:F71 D73:F81 D83:F91 D93:F101 D103:F110 D112:F127 K6:L12 K14:L21 K23:L31 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 N5:R12 Q14:R21 Q23:R31 Q33:R41 Q43:R51 Q53:R61 Q63:R71 Q73:R81 Q83:R91 Q93:R101 Q103:R110 Q113:Q126 R113:R127" name="LAS"/>
+    <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M31 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110 M33:M41 M43:M110" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="4">
@@ -14322,15 +14140,18 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 X103:X110 X83:X91 X93:X101 X14:X21 X5:X12 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
       <formula1>"2024,2025"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G103:G110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 M14:M31 M33:M41 M43:M110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F12 F14:F21 F23:F31 F33:F41 F43:F51 F53:F61 F63:F71 F73:F81 F83:F91 F93:F101 F103:F110 F112:F127 L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61 L63:L71 L73:L81 L83:L91 L93:L101 L103:L110 L112:L127 R5:R12 R14:R21 R23:R31 R33:R41 R43:R51 R53:R61 R63:R71 R73:R81 R83:R91 R93:R101 R103:R110 R112:R127" xr:uid="{6DCE7706-0DE0-4CF8-9E96-B1DD61D06731}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14346,7 +14167,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -14492,7 +14313,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="19.149999999999999">
+    <row r="3" spans="1:27" ht="38.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -14561,7 +14382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="19.149999999999999">
+    <row r="4" spans="1:27" ht="19.5">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -14630,7 +14451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999">
+    <row r="5" spans="1:27" ht="19.5">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -14699,7 +14520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999">
+    <row r="6" spans="1:27" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -14768,7 +14589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999">
+    <row r="7" spans="1:27" ht="19.5">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -14837,7 +14658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999">
+    <row r="8" spans="1:27" ht="19.5">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -14906,7 +14727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999">
+    <row r="9" spans="1:27" ht="19.5">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -14975,7 +14796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999">
+    <row r="10" spans="1:27" ht="19.5">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -15114,7 +14935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="19.149999999999999">
+    <row r="13" spans="1:27" ht="19.5">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -15183,7 +15004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999">
+    <row r="14" spans="1:27" ht="19.5">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -15252,7 +15073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999">
+    <row r="15" spans="1:27" ht="19.5">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -15321,7 +15142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999">
+    <row r="16" spans="1:27" ht="19.5">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -15390,7 +15211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999">
+    <row r="17" spans="1:27" ht="19.5">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -15459,7 +15280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999">
+    <row r="18" spans="1:27" ht="19.5">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -15528,7 +15349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999">
+    <row r="19" spans="1:27" ht="19.5">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -15667,7 +15488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="19.149999999999999">
+    <row r="22" spans="1:27" ht="19.5">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -15736,7 +15557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999">
+    <row r="23" spans="1:27" ht="19.5">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -15805,7 +15626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999">
+    <row r="24" spans="1:27" ht="19.5">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -15874,7 +15695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999">
+    <row r="25" spans="1:27" ht="19.5">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -15943,7 +15764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999">
+    <row r="26" spans="1:27" ht="19.5">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -16012,7 +15833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999">
+    <row r="27" spans="1:27" ht="19.5">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -16081,7 +15902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999">
+    <row r="28" spans="1:27" ht="19.5">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -16150,7 +15971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999">
+    <row r="29" spans="1:27" ht="19.5">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -16220,7 +16041,7 @@
       </c>
     </row>
     <row r="30" spans="1:27" s="7" customFormat="1"/>
-    <row r="31" spans="1:27" ht="19.149999999999999">
+    <row r="31" spans="1:27" ht="19.5">
       <c r="A31" s="1">
         <v>4</v>
       </c>
@@ -16289,7 +16110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="19.149999999999999">
+    <row r="32" spans="1:27" ht="19.5">
       <c r="A32" s="1">
         <v>4</v>
       </c>
@@ -16358,7 +16179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999">
+    <row r="33" spans="1:27" ht="19.5">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -16427,7 +16248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999">
+    <row r="34" spans="1:27" ht="19.5">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -16496,7 +16317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999">
+    <row r="35" spans="1:27" ht="38.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -16565,7 +16386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999">
+    <row r="36" spans="1:27" ht="19.5">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -16634,7 +16455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999">
+    <row r="37" spans="1:27" ht="19.5">
       <c r="A37" s="37">
         <v>4</v>
       </c>
@@ -16703,7 +16524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999">
+    <row r="38" spans="1:27" ht="19.5">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -16772,7 +16593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999">
+    <row r="39" spans="1:27" ht="19.5">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -16841,7 +16662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999">
+    <row r="40" spans="1:27" ht="19.5">
       <c r="A40" s="37">
         <v>4</v>
       </c>
@@ -16910,7 +16731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999">
+    <row r="41" spans="1:27" ht="19.5">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -16980,7 +16801,7 @@
       </c>
     </row>
     <row r="42" spans="1:27" s="7" customFormat="1"/>
-    <row r="43" spans="1:27" ht="19.149999999999999">
+    <row r="43" spans="1:27" ht="19.5">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -17049,7 +16870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999">
+    <row r="44" spans="1:27" ht="19.5">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -17118,7 +16939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="19.5">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -17187,7 +17008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999">
+    <row r="46" spans="1:27" ht="19.5">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -17256,7 +17077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="38.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -17325,7 +17146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999">
+    <row r="48" spans="1:27" ht="19.5">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -17394,7 +17215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999">
+    <row r="49" spans="1:27" ht="19.5">
       <c r="A49" s="37">
         <v>5</v>
       </c>
@@ -17463,7 +17284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999">
+    <row r="50" spans="1:27" ht="19.5">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -17532,7 +17353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999">
+    <row r="51" spans="1:27" ht="19.5">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -17601,7 +17422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="19.149999999999999">
+    <row r="52" spans="1:27" ht="19.5">
       <c r="A52" s="37">
         <v>5</v>
       </c>
@@ -17670,7 +17491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999">
+    <row r="53" spans="1:27" ht="19.5">
       <c r="A53" s="1">
         <v>5</v>
       </c>
@@ -17740,7 +17561,7 @@
       </c>
     </row>
     <row r="54" spans="1:27" s="7" customFormat="1"/>
-    <row r="55" spans="1:27" ht="19.149999999999999">
+    <row r="55" spans="1:27" ht="19.5">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -17809,7 +17630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999">
+    <row r="56" spans="1:27" ht="19.5">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -17878,7 +17699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999">
+    <row r="57" spans="1:27" ht="19.5">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -17947,7 +17768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999">
+    <row r="58" spans="1:27" ht="19.5">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -18016,7 +17837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999">
+    <row r="59" spans="1:27" ht="38.25">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -18085,7 +17906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999">
+    <row r="60" spans="1:27" ht="19.5">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -18154,7 +17975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999">
+    <row r="61" spans="1:27" ht="19.5">
       <c r="A61" s="37">
         <v>6</v>
       </c>
@@ -18223,7 +18044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="19.149999999999999">
+    <row r="62" spans="1:27" ht="19.5">
       <c r="A62" s="1">
         <v>6</v>
       </c>
@@ -18292,7 +18113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
+    <row r="63" spans="1:27" ht="19.5">
       <c r="A63" s="1">
         <v>6</v>
       </c>
@@ -18361,7 +18182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
+    <row r="64" spans="1:27" ht="19.5">
       <c r="A64" s="37">
         <v>6</v>
       </c>
@@ -18430,7 +18251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
+    <row r="65" spans="1:27" ht="19.5">
       <c r="A65" s="1">
         <v>6</v>
       </c>
@@ -18500,7 +18321,7 @@
       </c>
     </row>
     <row r="66" spans="1:27" s="7" customFormat="1"/>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="67" spans="1:27" ht="19.5">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -18569,7 +18390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="19.5">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -18638,7 +18459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="19.5">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -18707,7 +18528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="19.5">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -18776,7 +18597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="38.25">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -18845,7 +18666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="19.149999999999999">
+    <row r="72" spans="1:27" ht="19.5">
       <c r="A72" s="10">
         <v>7</v>
       </c>
@@ -18914,7 +18735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="19.5">
       <c r="A73" s="38">
         <v>7</v>
       </c>
@@ -18983,7 +18804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="19.5">
       <c r="A74" s="10">
         <v>7</v>
       </c>
@@ -19052,7 +18873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="19.5">
       <c r="A75" s="10">
         <v>7</v>
       </c>
@@ -19121,7 +18942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="19.5">
       <c r="A76" s="38">
         <v>7</v>
       </c>
@@ -19190,7 +19011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="19.5">
       <c r="A77" s="10">
         <v>7</v>
       </c>
@@ -19260,7 +19081,7 @@
       </c>
     </row>
     <row r="78" spans="1:27" s="7" customFormat="1"/>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="79" spans="1:27" ht="19.5">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -19329,7 +19150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="19.5">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -19398,7 +19219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="19.5">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -19467,7 +19288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="19.149999999999999">
+    <row r="82" spans="1:27" ht="19.5">
       <c r="A82" s="10">
         <v>8</v>
       </c>
@@ -19536,7 +19357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="19.5">
       <c r="A83" s="10">
         <v>8</v>
       </c>
@@ -19605,7 +19426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="19.5">
       <c r="A84" s="10">
         <v>8</v>
       </c>
@@ -19674,7 +19495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="19.5">
       <c r="A85" s="38">
         <v>8</v>
       </c>
@@ -19743,7 +19564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="19.5">
       <c r="A86" s="10">
         <v>8</v>
       </c>
@@ -19812,7 +19633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="19.5">
       <c r="A87" s="10">
         <v>8</v>
       </c>
@@ -19881,7 +19702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="19.5">
       <c r="A88" s="38">
         <v>8</v>
       </c>
@@ -19950,7 +19771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="19.5">
       <c r="A89" s="10">
         <v>8</v>
       </c>
@@ -20020,7 +19841,7 @@
       </c>
     </row>
     <row r="90" spans="1:27" s="7" customFormat="1"/>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="91" spans="1:27" ht="19.5">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -20089,7 +19910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="19.149999999999999">
+    <row r="92" spans="1:27" ht="19.5">
       <c r="A92" s="10">
         <v>9</v>
       </c>
@@ -20158,7 +19979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="19.5">
       <c r="A93" s="10">
         <v>9</v>
       </c>
@@ -20227,7 +20048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="19.5">
       <c r="A94" s="10">
         <v>9</v>
       </c>
@@ -20296,7 +20117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="19.5">
       <c r="A95" s="10">
         <v>9</v>
       </c>
@@ -20365,7 +20186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="19.5">
       <c r="A96" s="10">
         <v>9</v>
       </c>
@@ -20434,7 +20255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="19.5">
       <c r="A97" s="38">
         <v>9</v>
       </c>
@@ -20503,7 +20324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="19.5">
       <c r="A98" s="10">
         <v>9</v>
       </c>
@@ -20572,7 +20393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="19.5">
       <c r="A99" s="10">
         <v>9</v>
       </c>
@@ -20641,7 +20462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
+    <row r="100" spans="1:27" ht="19.5">
       <c r="A100" s="38">
         <v>9</v>
       </c>
@@ -20710,7 +20531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="19.5">
       <c r="A101" s="10">
         <v>9</v>
       </c>
@@ -20779,8 +20600,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1"/>
-    <row r="103" spans="1:27" ht="19.149999999999999">
+    <row r="102" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="103" spans="1:27" ht="19.5">
       <c r="A103" s="10">
         <v>10</v>
       </c>
@@ -20849,7 +20670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="19.5">
       <c r="A104" s="10">
         <v>10</v>
       </c>
@@ -20918,7 +20739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="19.5">
       <c r="A105" s="10">
         <v>10</v>
       </c>
@@ -20987,7 +20808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="19.5">
       <c r="A106" s="10">
         <v>10</v>
       </c>
@@ -21056,7 +20877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="19.149999999999999">
+    <row r="107" spans="1:27" ht="19.5">
       <c r="A107" s="10">
         <v>10</v>
       </c>
@@ -21125,7 +20946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="19.5">
       <c r="A108" s="10">
         <v>10</v>
       </c>
@@ -21194,7 +21015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="19.149999999999999">
+    <row r="109" spans="1:27" ht="19.5">
       <c r="A109" s="38">
         <v>10</v>
       </c>
@@ -21263,7 +21084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="19.149999999999999">
+    <row r="110" spans="1:27" ht="19.5">
       <c r="A110" s="10">
         <v>10</v>
       </c>
@@ -21332,7 +21153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="19.149999999999999">
+    <row r="111" spans="1:27" ht="19.5">
       <c r="A111" s="10">
         <v>10</v>
       </c>
@@ -21401,7 +21222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
+    <row r="112" spans="1:27" ht="19.5">
       <c r="A112" s="38">
         <v>10</v>
       </c>
@@ -21470,7 +21291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="19.149999999999999">
+    <row r="113" spans="1:28" ht="19.5">
       <c r="A113" s="10">
         <v>10</v>
       </c>
@@ -21540,7 +21361,7 @@
       </c>
     </row>
     <row r="114" spans="1:28" s="7" customFormat="1"/>
-    <row r="115" spans="1:28" ht="38.450000000000003">
+    <row r="115" spans="1:28" ht="38.25">
       <c r="A115" s="1" t="s">
         <v>29</v>
       </c>
@@ -21609,7 +21430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="19.149999999999999">
+    <row r="116" spans="1:28" ht="19.5">
       <c r="A116" s="1" t="s">
         <v>29</v>
       </c>
@@ -21678,7 +21499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="19.149999999999999">
+    <row r="117" spans="1:28" ht="19.5">
       <c r="A117" s="1" t="s">
         <v>29</v>
       </c>
@@ -21747,7 +21568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:28" ht="19.149999999999999">
+    <row r="118" spans="1:28" ht="19.5">
       <c r="A118" s="1" t="s">
         <v>29</v>
       </c>
@@ -21816,7 +21637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="38.450000000000003">
+    <row r="119" spans="1:28" ht="38.25">
       <c r="A119" s="1" t="s">
         <v>29</v>
       </c>
@@ -21885,7 +21706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:28" ht="19.149999999999999">
+    <row r="120" spans="1:28" ht="38.25">
       <c r="A120" s="1" t="s">
         <v>29</v>
       </c>
@@ -21954,7 +21775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:28" ht="38.450000000000003">
+    <row r="121" spans="1:28" ht="57.75">
       <c r="A121" s="1" t="s">
         <v>29</v>
       </c>
@@ -22023,7 +21844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="38.450000000000003">
+    <row r="122" spans="1:28" ht="38.25">
       <c r="A122" s="1" t="s">
         <v>29</v>
       </c>
@@ -22603,190 +22424,10 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
-    <protectedRange sqref="J2:L2 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D79:F89 D91:F101 D115:F122 P2:R10 N3:O10 V2:X10 T3:U10 N12:R19 T12:X19 H3:L10 Z3:AA10 Z12:AA19 H12:L19 N21:R29 T21:X29 Z21:AA29 H21:L29 T31:X41 Z31:AA41 H31:L41 T43:X53 Z43:AA53 H43:L53 T55:X65 Z55:AA65 H55:L65 T67:X77 Z67:AA77 H67:L77 T79:X89 Z79:AA89 H79:L89 T91:X101 Z91:AA101 H91:L101 T103:X113 Z103:AA113 H103:L113 N115:R122 T115:X122 Z115:AA122 H115:L122 D103:F113 N31:R41 N43:R53 N55:R65 N67:R77 N79:R89 N91:R101 N103:R113" name="LAS"/>
+    <protectedRange sqref="J2:L2 N3:O10 T3:U10 Z3:AA10 Z12:AA19 Z21:AA29 Z31:AA41 Z43:AA53 Z55:AA65 Z67:AA77 Z79:AA89 Z91:AA101 Z103:AA113 Z115:AA122 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D79:F89 D91:F101 D103:F113 D115:F122 H3:L10 H12:L19 H21:L29 H31:L41 H43:L53 H55:L65 H67:L77 H79:L89 H91:L101 H103:L113 H115:L122 P2:R10 N12:R19 N21:R29 N31:R41 N43:R53 N55:R65 N67:R77 N79:R89 N91:R101 N103:R113 N115:R122 V2:X10 T12:X19 T21:X29 T31:X41 T43:X53 T55:X65 T67:X77 T79:X89 T91:X101 T103:X113 T115:X122" name="LAS"/>
     <protectedRange sqref="G2:I2 M2:O2 S2:U2 Y2:AA2 G3:G10 M3:M10 S3:S10 Y3:Y10 Y12:Y19 G12:G19 M12:M19 S12:S19 Y21:Y29 G21:G29 M21:M29 S21:S29 Y31:Y41 G31:G41 M31:M41 S31:S41 Y43:Y53 G43:G53 M43:M53 S43:S53 Y55:Y65 G55:G65 M55:M65 S55:S65 Y67:Y77 G67:G77 M67:M77 S67:S77 Y79:Y89 G79:G89 M79:M89 S79:S89 Y91:Y101 G91:G101 M91:M101 S91:S101 Y103:Y113 G103:G113 M103:M113 S103:S113 Y115:Y122 G115:G122 M115:M122 S115:S122" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
@@ -22796,12 +22437,18 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F10 F12:F19 F21:F29" xr:uid="{D17A4C61-3F4B-4139-9249-B0373325F473}">
+      <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F31:F41 F43:F53 F55:F65 F67:F77 F79:F89 F91:F101 F103:F113 F115:F122 L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 L67:L77 L79:L89 L91:L101 L103:L113 L115:L122 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R55:R65 R67:R77 R79:R89 R91:R101 R103:R113 R115:R122 X3:X10 X12:X19 X21:X29 X31:X41 X43:X53 X55:X65 X67:X77 X79:X89 X91:X101 X103:X113" xr:uid="{61577BFD-628C-4C89-9AA5-0A9FC417321E}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
